--- a/main/StructureDefinition-bc-metadata-parameters-in.xlsx
+++ b/main/StructureDefinition-bc-metadata-parameters-in.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -929,7 +929,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="30.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="35.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="39.13671875" customWidth="true" bestFit="true"/>
@@ -2455,7 +2455,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>156</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>161</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>162</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>165</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>170</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>175</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>180</v>
       </c>
@@ -5037,12 +5037,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL38">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
